--- a/fix-errors/ig/FRMedicationRequestLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRMedicationRequestLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-prescription-item</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-prescription-item|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-traitement-prescrit</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-traitement-prescrit|0.1.0</t>
   </si>
   <si>
     <t>FRLMPrescriptionItem</t>
@@ -310,7 +310,7 @@
     <t>FRCDATraitementPrescrit.entryRelationship:frNonRemboursable</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-request-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-request-document|0.1.0</t>
   </si>
   <si>
     <t>FRMedicationRequestDocument</t>
